--- a/artfynd/A 3380-2023 artfynd.xlsx
+++ b/artfynd/A 3380-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3380-2023 artfynd.xlsx
+++ b/artfynd/A 3380-2023 artfynd.xlsx
@@ -1158,7 +1158,7 @@
         <v>109918259</v>
       </c>
       <c r="B6" t="n">
-        <v>56683</v>
+        <v>56689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>109918539</v>
       </c>
       <c r="B14" t="n">
-        <v>56683</v>
+        <v>56689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 3380-2023 artfynd.xlsx
+++ b/artfynd/A 3380-2023 artfynd.xlsx
@@ -1158,7 +1158,7 @@
         <v>109918259</v>
       </c>
       <c r="B6" t="n">
-        <v>56689</v>
+        <v>56692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>109918539</v>
       </c>
       <c r="B14" t="n">
-        <v>56689</v>
+        <v>56692</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 3380-2023 artfynd.xlsx
+++ b/artfynd/A 3380-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,121 +2802,6 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>113349344</v>
-      </c>
-      <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Vegalla-Mögöl, Ög</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>568834</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6463768</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Björsäter</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>E-Åtv-0247</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Monika Sunhede</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3380-2023 artfynd.xlsx
+++ b/artfynd/A 3380-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,44 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109918150</v>
+        <v>109918481</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -723,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568869.7445172874</v>
+        <v>568633</v>
       </c>
       <c r="R2" t="n">
-        <v>6463750.870542201</v>
+        <v>6463796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,47 +777,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109918139</v>
+        <v>109918209</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568854.8141402922</v>
+        <v>568829</v>
       </c>
       <c r="R3" t="n">
-        <v>6463761.646119289</v>
+        <v>6463769</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,28 +853,17 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -917,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109918481</v>
+        <v>109918474</v>
       </c>
       <c r="B4" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,27 +893,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>102118</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568632.5538550223</v>
+        <v>568633</v>
       </c>
       <c r="R4" t="n">
-        <v>6463796.136809848</v>
+        <v>6463796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,28 +954,17 @@
           <t>2023-06-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,47 +983,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109918199</v>
+        <v>109918259</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568794.9202671768</v>
+        <v>568739</v>
       </c>
       <c r="R5" t="n">
-        <v>6463754.29484093</v>
+        <v>6463773</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,28 +1055,17 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1155,19 +1084,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109918259</v>
+        <v>109918539</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1199,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568739</v>
+        <v>568638</v>
       </c>
       <c r="R6" t="n">
-        <v>6463773</v>
+        <v>6463763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,47 +1185,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109918175</v>
+        <v>109918211</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1309,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568814.5641690375</v>
+        <v>568779</v>
       </c>
       <c r="R7" t="n">
-        <v>6463775.133166678</v>
+        <v>6463773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,28 +1257,17 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1382,47 +1286,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109918121</v>
+        <v>109918493</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1430,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568833.6501726537</v>
+        <v>568619</v>
       </c>
       <c r="R8" t="n">
-        <v>6463767.583173927</v>
+        <v>6463776</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,22 +1355,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1369,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1503,15 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109918202</v>
+        <v>109918088</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1417,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1551,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568755.6773560892</v>
+        <v>568868</v>
       </c>
       <c r="R9" t="n">
-        <v>6463770.427722292</v>
+        <v>6463767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,19 +1463,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,15 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109918088</v>
+        <v>109918108</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1523,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1672,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568867.88115721</v>
+        <v>568867</v>
       </c>
       <c r="R10" t="n">
-        <v>6463767.129521053</v>
+        <v>6463766</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,19 +1569,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,15 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109918188</v>
+        <v>109918121</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1629,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1793,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568796.5950650965</v>
+        <v>568834</v>
       </c>
       <c r="R11" t="n">
-        <v>6463779.024007019</v>
+        <v>6463768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,19 +1675,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,40 +1705,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109918224</v>
+        <v>109918127</v>
       </c>
       <c r="B12" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1910,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568747.6356536957</v>
+        <v>568865</v>
       </c>
       <c r="R12" t="n">
-        <v>6463778.696054157</v>
+        <v>6463774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,19 +1781,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,15 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109918160</v>
+        <v>109918139</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +1841,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -2031,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568872.8842772871</v>
+        <v>568855</v>
       </c>
       <c r="R13" t="n">
-        <v>6463751.976421326</v>
+        <v>6463762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2064,19 +1887,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2104,43 +1917,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109918539</v>
+        <v>109918150</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2148,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568638</v>
+        <v>568870</v>
       </c>
       <c r="R14" t="n">
-        <v>6463763</v>
+        <v>6463751</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,12 +1990,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,6 +2004,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2210,43 +2023,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109918493</v>
+        <v>109918160</v>
       </c>
       <c r="B15" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2254,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568618.689801628</v>
+        <v>568873</v>
       </c>
       <c r="R15" t="n">
-        <v>6463775.925592254</v>
+        <v>6463752</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,22 +2096,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,6 +2110,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2326,43 +2129,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109918211</v>
+        <v>109918175</v>
       </c>
       <c r="B16" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2370,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568778.8000262105</v>
+        <v>568815</v>
       </c>
       <c r="R16" t="n">
-        <v>6463772.932898336</v>
+        <v>6463775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,27 +2205,18 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2442,15 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109918127</v>
+        <v>109918188</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2265,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2490,10 +2278,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568864.6038461279</v>
+        <v>568797</v>
       </c>
       <c r="R17" t="n">
-        <v>6463773.904213835</v>
+        <v>6463779</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,19 +2311,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2563,15 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109918108</v>
+        <v>109918199</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2371,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2611,10 +2384,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568866.8468024585</v>
+        <v>568795</v>
       </c>
       <c r="R18" t="n">
-        <v>6463766.060401879</v>
+        <v>6463754</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,19 +2417,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2684,47 +2447,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109918209</v>
+        <v>109918202</v>
       </c>
       <c r="B19" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2732,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568828.8947052784</v>
+        <v>568756</v>
       </c>
       <c r="R19" t="n">
-        <v>6463768.551265683</v>
+        <v>6463770</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,27 +2523,18 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2801,6 +2550,108 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>109918224</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vegalla-Mögöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>568748</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6463779</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3380-2023 artfynd.xlsx
+++ b/artfynd/A 3380-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918481</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918209</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918474</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918259</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918539</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918211</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918493</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918088</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918108</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918121</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918127</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1914,6 +1974,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918139</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2020,6 +2085,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918150</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2126,6 +2196,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918160</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2232,6 +2307,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918175</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2338,6 +2418,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918188</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2444,6 +2529,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918199</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2550,6 +2640,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918202</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2652,8 +2747,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109918224</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>